--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig4_subscore_distribution_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig4_subscore_distribution_data.xlsx
@@ -444,7 +444,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-8fdd3599890f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig4_subscore_distribution_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig4_subscore_distribution_data.xlsx
@@ -444,7 +444,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-8fdd3599890f</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
